--- a/data/s4/Annelinn/archetypes/stats_trans.xlsx
+++ b/data/s4/Annelinn/archetypes/stats_trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s4\Annelinn\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B3CFF5-2F60-4718-8A4C-2EA06AD5D21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5C7A2E-0B33-472E-AF97-4DE890845937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,12 +89,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -124,11 +130,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,8 +488,8 @@
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3">
-        <v>0.8</v>
+      <c r="C3" s="2">
+        <v>0.4</v>
       </c>
       <c r="D3">
         <v>0.03</v>
@@ -521,8 +528,8 @@
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5">
-        <v>0.8</v>
+      <c r="C5" s="2">
+        <v>0.4</v>
       </c>
       <c r="D5">
         <v>0.03</v>
@@ -561,8 +568,8 @@
       <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7">
-        <v>0.8</v>
+      <c r="C7" s="2">
+        <v>0.4</v>
       </c>
       <c r="D7">
         <v>0.03</v>
@@ -601,8 +608,8 @@
       <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="C9">
-        <v>0.8</v>
+      <c r="C9" s="2">
+        <v>0.4</v>
       </c>
       <c r="D9">
         <v>0.03</v>
@@ -641,8 +648,8 @@
       <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="C11">
-        <v>0.8</v>
+      <c r="C11" s="2">
+        <v>0.4</v>
       </c>
       <c r="D11">
         <v>0.04</v>
@@ -681,8 +688,8 @@
       <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="C13">
-        <v>0.8</v>
+      <c r="C13" s="2">
+        <v>0.4</v>
       </c>
       <c r="D13">
         <v>0.03</v>
@@ -721,8 +728,8 @@
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15">
-        <v>0.8</v>
+      <c r="C15" s="2">
+        <v>0.4</v>
       </c>
       <c r="D15">
         <v>0.04</v>
@@ -761,8 +768,8 @@
       <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="C17">
-        <v>0.8</v>
+      <c r="C17" s="2">
+        <v>0.4</v>
       </c>
       <c r="D17">
         <v>0.05</v>
